--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487711_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487711_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7358</v>
+        <v>2.718</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4533</v>
+        <v>3.6535</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7175</v>
+        <v>-0.9355</v>
       </c>
       <c r="G2" t="n">
         <v>2.8591</v>
@@ -610,13 +610,13 @@
         <v>0.9702</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4603</v>
+        <v>0.4425</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1683</v>
+        <v>0.0319</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6286</v>
+        <v>0.4105</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5537</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>D. TOLOSA OROPESA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0558</v>
+        <v>0.6492</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1011</v>
+        <v>2.3135</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0453</v>
+        <v>-1.6644</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6476</v>
+        <v>1.5526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4441</v>
+        <v>2.8283</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2035</v>
+        <v>-1.2757</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6626</v>
+        <v>3.2888</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3635</v>
+        <v>2.657</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2991</v>
+        <v>0.6318</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.015</v>
+        <v>-1.7362</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9195</v>
+        <v>0.1714</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0956</v>
+        <v>-1.9075</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8261</v>
+        <v>-0.0393</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4087</v>
+        <v>-0.0051</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4175</v>
+        <v>-0.0342</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. TOLOSA OROPESA</t>
+          <t>D. RUEDA ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5496</v>
+        <v>0.2049</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5137</v>
+        <v>0.7705</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9642</v>
+        <v>-0.5657</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5526</v>
+        <v>0.4628</v>
       </c>
       <c r="H4" t="n">
-        <v>2.8283</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2757</v>
+        <v>-0.5044</v>
       </c>
       <c r="J4" t="n">
-        <v>3.2888</v>
+        <v>0.6915</v>
       </c>
       <c r="K4" t="n">
-        <v>2.657</v>
+        <v>0.6509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6318</v>
+        <v>0.0406</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7362</v>
+        <v>-0.2286</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1714</v>
+        <v>0.3164</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9075</v>
+        <v>-0.545</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1389</v>
+        <v>-0.452</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1951</v>
+        <v>0.0791</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.334</v>
+        <v>-0.5311</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. RUEDA ALVAREZ</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0771</v>
+        <v>0.1822</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5703</v>
+        <v>2.2002</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6474</v>
+        <v>-2.0181</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4628</v>
+        <v>0.6476</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.4441</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5044</v>
+        <v>0.2035</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6915</v>
+        <v>2.6626</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6509</v>
+        <v>1.3635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0406</v>
+        <v>1.2991</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2286</v>
+        <v>-2.015</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3164</v>
+        <v>-0.9195</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.545</v>
+        <v>-1.0956</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>-0.194</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>0.194</v>
+        <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.734</v>
+        <v>0.9525</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1211</v>
+        <v>0.5078</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6128</v>
+        <v>0.4447</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. AYALA AYLLÓN</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9945000000000001</v>
+        <v>-1.0226</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3599</v>
+        <v>-0.284</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3544</v>
+        <v>-0.7386</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.114</v>
+        <v>-0.6859</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3044</v>
+        <v>0.0799</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8096</v>
+        <v>-0.7658</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4814</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4459</v>
+        <v>0.103</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0356</v>
+        <v>-0.6267</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6325</v>
+        <v>-0.1621</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8585</v>
+        <v>-0.0231</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.774</v>
+        <v>-0.139</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3031</v>
+        <v>-0.3367</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2288</v>
+        <v>0.2397</v>
       </c>
       <c r="U6" t="n">
-        <v>1.5319</v>
+        <v>-0.5765</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8462</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0701</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>J. AYALA AYLLÓN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3434</v>
+        <v>-1.4668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5459000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8893</v>
+        <v>-1.9267</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2673</v>
+        <v>-4.114</v>
       </c>
       <c r="H7" t="n">
-        <v>1.305</v>
+        <v>-2.3044</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0377</v>
+        <v>-1.8096</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0819</v>
+        <v>-1.4814</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3512</v>
+        <v>-1.4459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7307</v>
+        <v>-0.0356</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8146</v>
+        <v>-2.6325</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0462</v>
+        <v>-0.8585</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7685</v>
+        <v>-1.774</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3582</v>
+        <v>0.9702</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.8308</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1222</v>
+        <v>-0.1287</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5193</v>
+        <v>0.9595</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.894</v>
+        <v>0.8462</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>2.0701</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1761</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>J. TRUJILLO FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3774</v>
+        <v>-2.0141</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5843</v>
+        <v>-0.4847</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7931</v>
+        <v>-1.5294</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6859</v>
+        <v>-2.6859</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0799</v>
+        <v>-0.2785</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7658</v>
+        <v>-2.4074</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.282</v>
       </c>
       <c r="K8" t="n">
-        <v>0.103</v>
+        <v>0.3625</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6267</v>
+        <v>-0.6445</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1621</v>
+        <v>-2.4039</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0231</v>
+        <v>-0.641</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.139</v>
+        <v>-1.7629</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6916</v>
+        <v>-0.376</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0606</v>
+        <v>-0.2027</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.631</v>
+        <v>-0.1733</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.6597</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7988</v>
+        <v>-2.0281</v>
       </c>
       <c r="E9" t="n">
-        <v>1.4042</v>
+        <v>0.4063</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.203</v>
+        <v>-2.4344</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9184</v>
+        <v>0.2673</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0008</v>
+        <v>1.305</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9192</v>
+        <v>-1.0377</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4771</v>
+        <v>2.0819</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3553</v>
+        <v>1.3512</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1218</v>
+        <v>0.7307</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3954</v>
+        <v>-1.8146</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3545</v>
+        <v>-0.0462</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.041</v>
+        <v>-1.7685</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.8806</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.8508</v>
+        <v>-1.9403</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9405</v>
+        <v>-0.0432</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1541</v>
+        <v>-0.0174</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2135</v>
+        <v>-0.0258</v>
       </c>
       <c r="V9" t="n">
-        <v>3.0597</v>
+        <v>-0.894</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6238</v>
+        <v>0.2821</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5642</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TRUJILLO FERNÁNDEZ</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3111</v>
+        <v>-2.4573</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6454</v>
+        <v>0.664</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6657</v>
+        <v>-3.1212</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6859</v>
+        <v>-1.9184</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2785</v>
+        <v>0.0008</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4074</v>
+        <v>-1.9192</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.282</v>
+        <v>1.4771</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3625</v>
+        <v>1.3553</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6445</v>
+        <v>0.1218</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4039</v>
+        <v>-3.3954</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.641</v>
+        <v>-1.3545</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7629</v>
+        <v>-2.041</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3881</v>
+        <v>-3.8806</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-4.8508</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.2821</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3634</v>
+        <v>0.4138</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3095</v>
+        <v>-0.1318</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6597</v>
+        <v>3.0597</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.6238</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6597</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7089</v>
+        <v>-2.9209</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7307</v>
+        <v>-0.2698</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9782</v>
+        <v>-2.6511</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3691</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3219</v>
+        <v>-0.5339</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6057</v>
+        <v>-0.1447</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7161999999999999</v>
+        <v>-0.3892</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6597</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7512</v>
+        <v>-3.1723</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.0891</v>
+        <v>-1.7282</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6621</v>
+        <v>-1.4441</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4901</v>
@@ -1390,13 +1390,13 @@
         <v>0.194</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.485</v>
+        <v>0.0939</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2299</v>
+        <v>0.1309</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.255</v>
+        <v>-0.037</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.0245</v>
+        <v>-3.415</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2723</v>
+        <v>-1.7718</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7522</v>
+        <v>-1.6432</v>
       </c>
       <c r="G13" t="n">
         <v>-3.0059</v>
@@ -1468,13 +1468,13 @@
         <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8246</v>
+        <v>-0.2151</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7268</v>
+        <v>-0.2263</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0978</v>
+        <v>0.0112</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-15.0457</v>
+        <v>-14.7428</v>
       </c>
       <c r="E14" t="n">
-        <v>5.6266</v>
+        <v>5.929499999999999</v>
       </c>
       <c r="F14" t="n">
         <v>-20.6724</v>
@@ -1513,7 +1513,7 @@
         <v>-9.479900000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>7.3981</v>
+        <v>7.398099999999999</v>
       </c>
       <c r="I14" t="n">
         <v>-16.8781</v>
@@ -1531,7 +1531,7 @@
         <v>-20.5684</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.885700000000001</v>
+        <v>-4.8857</v>
       </c>
       <c r="O14" t="n">
         <v>-15.6828</v>
@@ -1546,13 +1546,13 @@
         <v>6.7912</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3026999999999995</v>
+        <v>0.6055999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3755000000000003</v>
+        <v>0.6783000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0724999999999999</v>
+        <v>-0.07300000000000002</v>
       </c>
       <c r="V14" t="n">
         <v>-0.04780000000000051</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1665</v>
+        <v>6.3389</v>
       </c>
       <c r="E15" t="n">
-        <v>8.0313</v>
+        <v>7.9312</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8648</v>
+        <v>-1.5923</v>
       </c>
       <c r="G15" t="n">
         <v>6.7252</v>
@@ -1624,13 +1624,13 @@
         <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0482</v>
+        <v>0.1242</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2434</v>
+        <v>0.1433</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2916</v>
+        <v>-0.0191</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1224</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6682</v>
+        <v>6.1931</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1433</v>
+        <v>4.6438</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5249</v>
+        <v>1.5493</v>
       </c>
       <c r="G16" t="n">
         <v>3.8692</v>
@@ -1702,13 +1702,13 @@
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8129</v>
+        <v>-0.288</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1508</v>
+        <v>-0.6503</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3378</v>
+        <v>0.3623</v>
       </c>
       <c r="V16" t="n">
         <v>1.8358</v>
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8748</v>
+        <v>4.3753</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2628</v>
+        <v>3.7633</v>
       </c>
       <c r="F17" t="n">
         <v>0.612</v>
@@ -1780,10 +1780,10 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3275</v>
+        <v>0.173</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2905</v>
+        <v>0.21</v>
       </c>
       <c r="U17" t="n">
         <v>-0.037</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.209</v>
+        <v>2.4181</v>
       </c>
       <c r="E18" t="n">
-        <v>3.1645</v>
+        <v>3.2646</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9554</v>
+        <v>-0.8464</v>
       </c>
       <c r="G18" t="n">
         <v>1.2539</v>
@@ -1858,13 +1858,13 @@
         <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2431</v>
+        <v>0.4523</v>
       </c>
       <c r="T18" t="n">
-        <v>0.074</v>
+        <v>0.1741</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1691</v>
+        <v>0.2782</v>
       </c>
       <c r="V18" t="n">
         <v>-0.4522</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1597</v>
+        <v>1.4294</v>
       </c>
       <c r="E19" t="n">
         <v>2.0937</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9341</v>
+        <v>-0.6643</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4192</v>
@@ -1936,13 +1936,13 @@
         <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5271</v>
+        <v>-0.2574</v>
       </c>
       <c r="T19" t="n">
         <v>0.0134</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5406</v>
+        <v>-0.2708</v>
       </c>
       <c r="V19" t="n">
         <v>0.9418</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8563</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="E20" t="n">
         <v>1.0561</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1998</v>
+        <v>-0.227</v>
       </c>
       <c r="G20" t="n">
         <v>0.884</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V20" t="n">
         <v>0.2821</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>G. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0236</v>
+        <v>-0.5881</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08210000000000001</v>
+        <v>-1.2087</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0585</v>
+        <v>0.6206</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3651</v>
+        <v>0.7245</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7504999999999999</v>
+        <v>-0.4128</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6145</v>
+        <v>1.1372</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0895</v>
+        <v>0.2977</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3749</v>
+        <v>0.0948</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4643</v>
+        <v>0.203</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2756</v>
+        <v>0.4267</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1254</v>
+        <v>-0.5075</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.1502</v>
+        <v>0.9343</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5523</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.194</v>
+        <v>-2.1344</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4006</v>
+        <v>0.2695</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3656</v>
+        <v>0.016</v>
       </c>
       <c r="U21" t="n">
-        <v>0.035</v>
+        <v>0.2535</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5642</v>
+        <v>-0.6119</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. LARDIES GUILLEN</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1788</v>
+        <v>-0.6526</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9084</v>
+        <v>-0.6186</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7296</v>
+        <v>-0.034</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7245</v>
+        <v>-1.3651</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4128</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1372</v>
+        <v>-0.6145</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2977</v>
+        <v>-0.0895</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0948</v>
+        <v>0.3749</v>
       </c>
       <c r="L22" t="n">
-        <v>0.203</v>
+        <v>-0.4643</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4267</v>
+        <v>-1.2756</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5075</v>
+        <v>-1.1254</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9343</v>
+        <v>-0.1502</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9702</v>
+        <v>1.5523</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1344</v>
+        <v>-0.194</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1642</v>
+        <v>1.7463</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6788</v>
+        <v>-0.2756</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3163</v>
+        <v>-0.3351</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3625</v>
+        <v>0.0595</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6119</v>
+        <v>-0.5642</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4351</v>
+        <v>-0.6536</v>
       </c>
       <c r="E23" t="n">
-        <v>1.5032</v>
+        <v>1.2029</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9382</v>
+        <v>-1.8565</v>
       </c>
       <c r="G23" t="n">
         <v>0.3945</v>
@@ -2248,13 +2248,13 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3943</v>
+        <v>0.1758</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6068</v>
+        <v>0.3065</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2124</v>
+        <v>-0.1307</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2239</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>D. FERNANDEZ CAÑAS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5457</v>
+        <v>-1.1821</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.9175</v>
+        <v>-0.2862</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3717</v>
+        <v>-0.8958</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5089</v>
+        <v>-2.717</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.4604</v>
+        <v>-2.4395</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9515</v>
+        <v>-0.2775</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.0158</v>
+        <v>-0.206</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.8506</v>
+        <v>-0.4902</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8348</v>
+        <v>0.2842</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4931</v>
+        <v>-2.511</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6099</v>
+        <v>-1.9493</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1168</v>
+        <v>-0.5617</v>
       </c>
       <c r="P24" t="n">
         <v>1.1642</v>
@@ -2326,28 +2326,28 @@
         <v>1.3582</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7348</v>
+        <v>-0.1666</v>
       </c>
       <c r="T24" t="n">
-        <v>1.1058</v>
+        <v>-0.1683</v>
       </c>
       <c r="U24" t="n">
-        <v>0.629</v>
+        <v>0.0017</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0641</v>
+        <v>0.5373</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1865</v>
+        <v>0.2821</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1224</v>
+        <v>0.2552</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ CAÑAS</t>
+          <t>J. DE DOMINGO GARAY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.871</v>
+        <v>-1.3845</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.087</v>
+        <v>0.1664</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.784</v>
+        <v>-1.5509</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.717</v>
+        <v>1.138</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4395</v>
+        <v>0.0708</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2775</v>
+        <v>1.0672</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.206</v>
+        <v>1.3727</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4902</v>
+        <v>0.7003</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2842</v>
+        <v>0.6724</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.511</v>
+        <v>-0.2346</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.9493</v>
+        <v>-0.6294</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5617</v>
+        <v>0.3948</v>
       </c>
       <c r="P25" t="n">
-        <v>1.1642</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.194</v>
+        <v>-1.1642</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8555</v>
+        <v>-0.5703</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9691</v>
+        <v>-0.0421</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1135</v>
+        <v>-0.5282</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5373</v>
+        <v>-1.1761</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0.2552</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. DE DOMINGO GARAY</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.8817</v>
+        <v>-1.41</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0338</v>
+        <v>-1.6182</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.8479</v>
+        <v>0.2082</v>
       </c>
       <c r="G26" t="n">
-        <v>1.138</v>
+        <v>-3.5089</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0708</v>
+        <v>-4.4604</v>
       </c>
       <c r="I26" t="n">
-        <v>1.0672</v>
+        <v>0.9515</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3727</v>
+        <v>-2.0158</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7003</v>
+        <v>-2.8506</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6724</v>
+        <v>0.8348</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2346</v>
+        <v>-1.4931</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.6294</v>
+        <v>-1.6099</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3948</v>
+        <v>0.1168</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0675</v>
+        <v>0.8706</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2423</v>
+        <v>0.4051</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8252</v>
+        <v>0.4655</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.1761</v>
+        <v>0.0641</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.1865</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.1761</v>
+        <v>-0.1224</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>15.04580000000001</v>
+        <v>15.713</v>
       </c>
       <c r="E27" t="n">
-        <v>20.3903</v>
+        <v>20.39029999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.3445</v>
+        <v>-4.6771</v>
       </c>
       <c r="G27" t="n">
         <v>9.479899999999999</v>
@@ -2551,7 +2551,7 @@
         <v>1.1954</v>
       </c>
       <c r="P27" t="n">
-        <v>5.821</v>
+        <v>5.821000000000001</v>
       </c>
       <c r="Q27" t="n">
         <v>-6.790999999999999</v>
@@ -2560,16 +2560,16 @@
         <v>12.612</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.3028000000000003</v>
+        <v>0.3645</v>
       </c>
       <c r="T27" t="n">
-        <v>0.07259999999999986</v>
+        <v>0.0726</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.3756000000000001</v>
+        <v>0.2919000000000001</v>
       </c>
       <c r="V27" t="n">
-        <v>0.0477000000000003</v>
+        <v>0.04770000000000003</v>
       </c>
       <c r="W27" t="n">
         <v>6.5402</v>
